--- a/docs/Plantilla_Gestion_Requerimientos_Scrum_RC.xlsx
+++ b/docs/Plantilla_Gestion_Requerimientos_Scrum_RC.xlsx
@@ -1,14 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\co-alumno\BioForjaRC_PaginaWeb\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD606CA1-53CA-4EC7-85A8-FF4F4A919BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Epicas" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Historias de Usuario" sheetId="2" r:id="rId5"/>
+    <sheet name="Epicas" sheetId="1" r:id="rId1"/>
+    <sheet name="Historias de Usuario" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="rssPePpxh9idr/8h5Pdh1NFrLJIS/AlC/28KJjGvEm8="/>
     </ext>
@@ -17,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="168">
   <si>
     <t>ID</t>
   </si>
@@ -503,32 +515,74 @@
   <si>
     <t>1. Permite modificar precio, descripción o fotos.
 2. Permite desactivar/pausar un producto sin eliminarlo.</t>
+  </si>
+  <si>
+    <t>EP-09</t>
+  </si>
+  <si>
+    <t>Métricas, Reportes e HistorialPanel de analítica comercial para el administrador y centro de historial de órdenes para el cliente.</t>
+  </si>
+  <si>
+    <t>Permitir al negocio analizar el rendimiento de ventas y brindar transparencia al cliente sobre sus transacciones pasadas.</t>
+  </si>
+  <si>
+    <t>HU-09.1</t>
+  </si>
+  <si>
+    <t>Consultar Historial de Pedidos</t>
+  </si>
+  <si>
+    <t>Consultar Reporte de Ventas y Rendimiento</t>
+  </si>
+  <si>
+    <t>Visualizar el listado y detalle de todos mis pedidos realizados</t>
+  </si>
+  <si>
+    <t>Visualizar un panel con total de ventas, productos más vendidos e ingresos por periodo</t>
+  </si>
+  <si>
+    <t>Revisar mis comprobantes, estados de despacho e historial de compras anteriores</t>
+  </si>
+  <si>
+    <t>Analizar el rendimiento comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Muestra fecha, número de orden, monto total y estado del envío.
+2. Permite descargar o ver la boleta comprobante </t>
+  </si>
+  <si>
+    <t>1. Despliega indicadores clave (ingresos diarios/mensuales y Top 5 de productos más vendidos).
+2. Permite filtrar los datos por rango de fechas y exportar a Excel/PDF.</t>
+  </si>
+  <si>
+    <t>Panel de analítica comercial para el administrador y centro de historial de compras para el cliente.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="4">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
     </font>
@@ -538,7 +592,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -548,83 +602,167 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="21">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC1E4F5"/>
-          <bgColor rgb="FFC1E4F5"/>
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <font>
+        <b/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -649,124 +787,140 @@
       </border>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
-          <bgColor rgb="FFFFF2CC"/>
+          <fgColor rgb="FFC1E4F5"/>
+          <bgColor rgb="FFC1E4F5"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFD4D4D4"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFD4D4D4"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
+          <fgColor rgb="FFC1E4F5"/>
+          <bgColor rgb="FFC1E4F5"/>
         </patternFill>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle count="4" pivot="0" name="Epicas-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Epicas-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="firstRowStripe" dxfId="19"/>
+      <tableStyleElement type="secondRowStripe" dxfId="18"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Historias de Usuario-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Historias de Usuario-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="13"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="secondRowStripe" dxfId="14"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H101" displayName="TablaEpicas" name="TablaEpicas" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEpicas" displayName="TablaEpicas" ref="A1:H101">
   <tableColumns count="8">
-    <tableColumn name="ID" id="1"/>
-    <tableColumn name="Épica" id="2"/>
-    <tableColumn name="Descripción" id="3"/>
-    <tableColumn name="Objetivo / Valor" id="4"/>
-    <tableColumn name="Prioridad" id="5"/>
-    <tableColumn name="Estado" id="6"/>
-    <tableColumn name="Responsable" id="7"/>
-    <tableColumn name="Observaciones" id="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Épica"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Descripción"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Objetivo / Valor"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Prioridad"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Estado"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Responsable"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Observaciones"/>
   </tableColumns>
-  <tableStyleInfo name="Epicas-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Epicas-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M201" displayName="TablaHistoriasUsuario" name="TablaHistoriasUsuario" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TablaHistoriasUsuario" displayName="TablaHistoriasUsuario" ref="A1:M201">
   <tableColumns count="13">
-    <tableColumn name="ID" id="1"/>
-    <tableColumn name="Épica" id="2"/>
-    <tableColumn name="Historia" id="3"/>
-    <tableColumn name="Como" id="4"/>
-    <tableColumn name="Quiero" id="5"/>
-    <tableColumn name="Para" id="6"/>
-    <tableColumn name="Prioridad" id="7"/>
-    <tableColumn name="Sprint" id="8"/>
-    <tableColumn name="Criterio de Aceptación" id="9"/>
-    <tableColumn name="Estado" id="10"/>
-    <tableColumn name="Review" id="11"/>
-    <tableColumn name="Responsable" id="12"/>
-    <tableColumn name="Observaciones" id="13"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Épica"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Historia"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Como"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Quiero"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Para"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Prioridad"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Sprint"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Criterio de Aceptación"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Estado"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Review"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Responsable"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Observaciones"/>
   </tableColumns>
-  <tableStyleInfo name="Historias de Usuario-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Historias de Usuario-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -956,28 +1110,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.0"/>
-    <col customWidth="1" min="2" max="2" width="24.0"/>
-    <col customWidth="1" min="3" max="3" width="43.88"/>
-    <col customWidth="1" min="4" max="4" width="43.13"/>
-    <col customWidth="1" min="5" max="5" width="14.0"/>
-    <col customWidth="1" min="6" max="6" width="18.0"/>
-    <col customWidth="1" min="7" max="7" width="22.0"/>
-    <col customWidth="1" min="8" max="8" width="34.0"/>
-    <col customWidth="1" min="9" max="26" width="8.75"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="43.875" customWidth="1"/>
+    <col min="4" max="4" width="43.125" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="26" width="8.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.0" customHeight="1">
+    <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1003,7 +1157,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="28.5" customHeight="1">
+    <row r="2" spans="1:8" ht="28.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1027,7 +1181,7 @@
       </c>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" ht="28.5" customHeight="1">
+    <row r="3" spans="1:8" ht="28.5" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1051,7 +1205,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" ht="28.5" customHeight="1">
+    <row r="4" spans="1:8" ht="28.5" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -1075,7 +1229,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" ht="28.5" customHeight="1">
+    <row r="5" spans="1:8" ht="28.5" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1099,7 +1253,7 @@
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" ht="28.5" customHeight="1">
+    <row r="6" spans="1:8" ht="28.5" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -1123,7 +1277,7 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" ht="28.5" customHeight="1">
+    <row r="7" spans="1:8" ht="28.5" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
@@ -1147,7 +1301,7 @@
       </c>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" ht="28.5" customHeight="1">
+    <row r="8" spans="1:8" ht="28.5" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>35</v>
       </c>
@@ -1171,7 +1325,7 @@
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" ht="28.5" customHeight="1">
+    <row r="9" spans="1:8" ht="28.5" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
@@ -1195,16 +1349,31 @@
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" ht="28.5" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="3"/>
+    <row r="10" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" ht="28.5" customHeight="1">
+    <row r="11" spans="1:8" ht="28.5" customHeight="1">
       <c r="A11" s="4"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1214,17 +1383,16 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" ht="28.5" customHeight="1">
+    <row r="12" spans="1:8" ht="28.5" customHeight="1">
       <c r="A12" s="4"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" ht="28.5" customHeight="1">
+    <row r="13" spans="1:8" ht="28.5" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1234,7 +1402,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" ht="28.5" customHeight="1">
+    <row r="14" spans="1:8" ht="28.5" customHeight="1">
       <c r="A14" s="4"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1244,7 +1412,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" ht="28.5" customHeight="1">
+    <row r="15" spans="1:8" ht="28.5" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1254,7 +1422,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" ht="28.5" customHeight="1">
+    <row r="16" spans="1:8" ht="28.5" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1264,7 +1432,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" ht="28.5" customHeight="1">
+    <row r="17" spans="1:8" ht="28.5" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1274,7 +1442,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" ht="28.5" customHeight="1">
+    <row r="18" spans="1:8" ht="28.5" customHeight="1">
       <c r="A18" s="4"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1284,7 +1452,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" ht="28.5" customHeight="1">
+    <row r="19" spans="1:8" ht="28.5" customHeight="1">
       <c r="A19" s="4"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1294,7 +1462,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" ht="28.5" customHeight="1">
+    <row r="20" spans="1:8" ht="28.5" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1304,7 +1472,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" ht="28.5" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1314,7 +1482,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" ht="28.5" customHeight="1">
+    <row r="22" spans="1:8" ht="28.5" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1324,7 +1492,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" ht="28.5" customHeight="1">
+    <row r="23" spans="1:8" ht="28.5" customHeight="1">
       <c r="A23" s="4"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1334,7 +1502,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" ht="28.5" customHeight="1">
+    <row r="24" spans="1:8" ht="28.5" customHeight="1">
       <c r="A24" s="4"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1344,7 +1512,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" ht="28.5" customHeight="1">
+    <row r="25" spans="1:8" ht="28.5" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1354,7 +1522,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" ht="28.5" customHeight="1">
+    <row r="26" spans="1:8" ht="28.5" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1364,7 +1532,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" ht="28.5" customHeight="1">
+    <row r="27" spans="1:8" ht="28.5" customHeight="1">
       <c r="A27" s="4"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1374,7 +1542,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" ht="28.5" customHeight="1">
+    <row r="28" spans="1:8" ht="28.5" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1384,7 +1552,7 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" ht="28.5" customHeight="1">
+    <row r="29" spans="1:8" ht="28.5" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -1394,7 +1562,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" ht="28.5" customHeight="1">
+    <row r="30" spans="1:8" ht="28.5" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -1404,7 +1572,7 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" ht="28.5" customHeight="1">
+    <row r="31" spans="1:8" ht="28.5" customHeight="1">
       <c r="A31" s="4"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1414,7 +1582,7 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" ht="28.5" customHeight="1">
+    <row r="32" spans="1:8" ht="28.5" customHeight="1">
       <c r="A32" s="4"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -1424,7 +1592,7 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" ht="28.5" customHeight="1">
+    <row r="33" spans="1:8" ht="28.5" customHeight="1">
       <c r="A33" s="4"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -1434,7 +1602,7 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" ht="28.5" customHeight="1">
+    <row r="34" spans="1:8" ht="28.5" customHeight="1">
       <c r="A34" s="4"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -1444,7 +1612,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" ht="28.5" customHeight="1">
+    <row r="35" spans="1:8" ht="28.5" customHeight="1">
       <c r="A35" s="4"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1454,7 +1622,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" ht="28.5" customHeight="1">
+    <row r="36" spans="1:8" ht="28.5" customHeight="1">
       <c r="A36" s="4"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1464,7 +1632,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" ht="28.5" customHeight="1">
+    <row r="37" spans="1:8" ht="28.5" customHeight="1">
       <c r="A37" s="4"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1474,7 +1642,7 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" ht="28.5" customHeight="1">
+    <row r="38" spans="1:8" ht="28.5" customHeight="1">
       <c r="A38" s="4"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1484,7 +1652,7 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" ht="28.5" customHeight="1">
+    <row r="39" spans="1:8" ht="28.5" customHeight="1">
       <c r="A39" s="4"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1494,7 +1662,7 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" ht="28.5" customHeight="1">
+    <row r="40" spans="1:8" ht="28.5" customHeight="1">
       <c r="A40" s="4"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -1504,7 +1672,7 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" ht="28.5" customHeight="1">
+    <row r="41" spans="1:8" ht="28.5" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1514,7 +1682,7 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" ht="28.5" customHeight="1">
+    <row r="42" spans="1:8" ht="28.5" customHeight="1">
       <c r="A42" s="4"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -1524,7 +1692,7 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" ht="28.5" customHeight="1">
+    <row r="43" spans="1:8" ht="28.5" customHeight="1">
       <c r="A43" s="4"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -1534,7 +1702,7 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" ht="28.5" customHeight="1">
+    <row r="44" spans="1:8" ht="28.5" customHeight="1">
       <c r="A44" s="4"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -1544,7 +1712,7 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" ht="28.5" customHeight="1">
+    <row r="45" spans="1:8" ht="28.5" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1554,7 +1722,7 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" ht="28.5" customHeight="1">
+    <row r="46" spans="1:8" ht="28.5" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -1564,7 +1732,7 @@
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" ht="28.5" customHeight="1">
+    <row r="47" spans="1:8" ht="28.5" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1574,7 +1742,7 @@
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" ht="28.5" customHeight="1">
+    <row r="48" spans="1:8" ht="28.5" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -1584,7 +1752,7 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" ht="28.5" customHeight="1">
+    <row r="49" spans="1:8" ht="28.5" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -1594,7 +1762,7 @@
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" ht="28.5" customHeight="1">
+    <row r="50" spans="1:8" ht="28.5" customHeight="1">
       <c r="A50" s="4"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -1604,7 +1772,7 @@
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" ht="28.5" customHeight="1">
+    <row r="51" spans="1:8" ht="28.5" customHeight="1">
       <c r="A51" s="4"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -1614,7 +1782,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" ht="28.5" customHeight="1">
+    <row r="52" spans="1:8" ht="28.5" customHeight="1">
       <c r="A52" s="4"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -1624,7 +1792,7 @@
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
     </row>
-    <row r="53" ht="28.5" customHeight="1">
+    <row r="53" spans="1:8" ht="28.5" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -1634,7 +1802,7 @@
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
     </row>
-    <row r="54" ht="28.5" customHeight="1">
+    <row r="54" spans="1:8" ht="28.5" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -1644,7 +1812,7 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
     </row>
-    <row r="55" ht="28.5" customHeight="1">
+    <row r="55" spans="1:8" ht="28.5" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -1654,7 +1822,7 @@
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" ht="28.5" customHeight="1">
+    <row r="56" spans="1:8" ht="28.5" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -1664,7 +1832,7 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" ht="28.5" customHeight="1">
+    <row r="57" spans="1:8" ht="28.5" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -1674,7 +1842,7 @@
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
     </row>
-    <row r="58" ht="28.5" customHeight="1">
+    <row r="58" spans="1:8" ht="28.5" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -1684,7 +1852,7 @@
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" ht="28.5" customHeight="1">
+    <row r="59" spans="1:8" ht="28.5" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -1694,7 +1862,7 @@
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
     </row>
-    <row r="60" ht="28.5" customHeight="1">
+    <row r="60" spans="1:8" ht="28.5" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -1704,7 +1872,7 @@
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
     </row>
-    <row r="61" ht="28.5" customHeight="1">
+    <row r="61" spans="1:8" ht="28.5" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -1714,7 +1882,7 @@
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" ht="28.5" customHeight="1">
+    <row r="62" spans="1:8" ht="28.5" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -1724,7 +1892,7 @@
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
     </row>
-    <row r="63" ht="28.5" customHeight="1">
+    <row r="63" spans="1:8" ht="28.5" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -1734,7 +1902,7 @@
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
     </row>
-    <row r="64" ht="28.5" customHeight="1">
+    <row r="64" spans="1:8" ht="28.5" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -1744,7 +1912,7 @@
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
     </row>
-    <row r="65" ht="28.5" customHeight="1">
+    <row r="65" spans="1:8" ht="28.5" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -1754,7 +1922,7 @@
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
     </row>
-    <row r="66" ht="28.5" customHeight="1">
+    <row r="66" spans="1:8" ht="28.5" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -1764,7 +1932,7 @@
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
     </row>
-    <row r="67" ht="28.5" customHeight="1">
+    <row r="67" spans="1:8" ht="28.5" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -1774,7 +1942,7 @@
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
     </row>
-    <row r="68" ht="28.5" customHeight="1">
+    <row r="68" spans="1:8" ht="28.5" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -1784,7 +1952,7 @@
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
     </row>
-    <row r="69" ht="28.5" customHeight="1">
+    <row r="69" spans="1:8" ht="28.5" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -1794,7 +1962,7 @@
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
     </row>
-    <row r="70" ht="28.5" customHeight="1">
+    <row r="70" spans="1:8" ht="28.5" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -1804,7 +1972,7 @@
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
     </row>
-    <row r="71" ht="28.5" customHeight="1">
+    <row r="71" spans="1:8" ht="28.5" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -1814,7 +1982,7 @@
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
     </row>
-    <row r="72" ht="28.5" customHeight="1">
+    <row r="72" spans="1:8" ht="28.5" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -1824,7 +1992,7 @@
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
     </row>
-    <row r="73" ht="28.5" customHeight="1">
+    <row r="73" spans="1:8" ht="28.5" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -1834,7 +2002,7 @@
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
     </row>
-    <row r="74" ht="28.5" customHeight="1">
+    <row r="74" spans="1:8" ht="28.5" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -1844,7 +2012,7 @@
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
     </row>
-    <row r="75" ht="28.5" customHeight="1">
+    <row r="75" spans="1:8" ht="28.5" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -1854,7 +2022,7 @@
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
     </row>
-    <row r="76" ht="28.5" customHeight="1">
+    <row r="76" spans="1:8" ht="28.5" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -1864,7 +2032,7 @@
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
     </row>
-    <row r="77" ht="28.5" customHeight="1">
+    <row r="77" spans="1:8" ht="28.5" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -1874,7 +2042,7 @@
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
     </row>
-    <row r="78" ht="28.5" customHeight="1">
+    <row r="78" spans="1:8" ht="28.5" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -1884,7 +2052,7 @@
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
     </row>
-    <row r="79" ht="28.5" customHeight="1">
+    <row r="79" spans="1:8" ht="28.5" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -1894,7 +2062,7 @@
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
     </row>
-    <row r="80" ht="28.5" customHeight="1">
+    <row r="80" spans="1:8" ht="28.5" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -1904,7 +2072,7 @@
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
     </row>
-    <row r="81" ht="28.5" customHeight="1">
+    <row r="81" spans="1:8" ht="28.5" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -1914,7 +2082,7 @@
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
     </row>
-    <row r="82" ht="28.5" customHeight="1">
+    <row r="82" spans="1:8" ht="28.5" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -1924,7 +2092,7 @@
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
     </row>
-    <row r="83" ht="28.5" customHeight="1">
+    <row r="83" spans="1:8" ht="28.5" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -1934,7 +2102,7 @@
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
     </row>
-    <row r="84" ht="28.5" customHeight="1">
+    <row r="84" spans="1:8" ht="28.5" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -1944,7 +2112,7 @@
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
     </row>
-    <row r="85" ht="28.5" customHeight="1">
+    <row r="85" spans="1:8" ht="28.5" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -1954,7 +2122,7 @@
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
     </row>
-    <row r="86" ht="28.5" customHeight="1">
+    <row r="86" spans="1:8" ht="28.5" customHeight="1">
       <c r="A86" s="4"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -1964,7 +2132,7 @@
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
     </row>
-    <row r="87" ht="28.5" customHeight="1">
+    <row r="87" spans="1:8" ht="28.5" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -1974,7 +2142,7 @@
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
     </row>
-    <row r="88" ht="28.5" customHeight="1">
+    <row r="88" spans="1:8" ht="28.5" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -1984,7 +2152,7 @@
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
     </row>
-    <row r="89" ht="28.5" customHeight="1">
+    <row r="89" spans="1:8" ht="28.5" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -1994,7 +2162,7 @@
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
     </row>
-    <row r="90" ht="28.5" customHeight="1">
+    <row r="90" spans="1:8" ht="28.5" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -2004,7 +2172,7 @@
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
     </row>
-    <row r="91" ht="28.5" customHeight="1">
+    <row r="91" spans="1:8" ht="28.5" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -2014,7 +2182,7 @@
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
     </row>
-    <row r="92" ht="28.5" customHeight="1">
+    <row r="92" spans="1:8" ht="28.5" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -2024,7 +2192,7 @@
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
     </row>
-    <row r="93" ht="28.5" customHeight="1">
+    <row r="93" spans="1:8" ht="28.5" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -2034,7 +2202,7 @@
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
     </row>
-    <row r="94" ht="28.5" customHeight="1">
+    <row r="94" spans="1:8" ht="28.5" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -2044,7 +2212,7 @@
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
     </row>
-    <row r="95" ht="28.5" customHeight="1">
+    <row r="95" spans="1:8" ht="28.5" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -2054,7 +2222,7 @@
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
     </row>
-    <row r="96" ht="28.5" customHeight="1">
+    <row r="96" spans="1:8" ht="28.5" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -2064,7 +2232,7 @@
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
     </row>
-    <row r="97" ht="28.5" customHeight="1">
+    <row r="97" spans="1:8" ht="28.5" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -2074,7 +2242,7 @@
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
     </row>
-    <row r="98" ht="28.5" customHeight="1">
+    <row r="98" spans="1:8" ht="28.5" customHeight="1">
       <c r="A98" s="4"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -2084,7 +2252,7 @@
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
     </row>
-    <row r="99" ht="28.5" customHeight="1">
+    <row r="99" spans="1:8" ht="28.5" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -2094,7 +2262,7 @@
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
     </row>
-    <row r="100" ht="28.5" customHeight="1">
+    <row r="100" spans="1:8" ht="28.5" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -2104,7 +2272,7 @@
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
     </row>
-    <row r="101" ht="28.5" customHeight="1">
+    <row r="101" spans="1:8" ht="28.5" customHeight="1">
       <c r="A101" s="4"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -2114,17 +2282,17 @@
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
     </row>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
-    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="102" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="103" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="104" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="105" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="106" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="107" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="108" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="109" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="110" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="111" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="112" spans="1:8" ht="14.25" customHeight="1"/>
     <row r="113" ht="14.25" customHeight="1"/>
     <row r="114" ht="14.25" customHeight="1"/>
     <row r="115" ht="14.25" customHeight="1"/>
@@ -3015,70 +3183,60 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="E2:E101">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>E2="Alta"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E101">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>E2="Media"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E101">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>E2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F101">
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>F2="Finalizada"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F101">
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="8" priority="5">
       <formula>F2="Bloqueada"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E101">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E101" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F101">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F101" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Pendiente,En análisis,Lista,En desarrollo,En revisión,Finalizada,Bloqueada"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:M1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.0"/>
-    <col customWidth="1" min="2" max="2" width="22.0"/>
-    <col customWidth="1" min="3" max="3" width="30.0"/>
-    <col customWidth="1" min="4" max="4" width="24.0"/>
-    <col customWidth="1" min="5" max="6" width="32.0"/>
-    <col customWidth="1" min="7" max="8" width="14.0"/>
-    <col customWidth="1" min="9" max="9" width="38.0"/>
-    <col customWidth="1" min="10" max="10" width="18.0"/>
-    <col customWidth="1" min="11" max="11" width="20.0"/>
-    <col customWidth="1" min="12" max="12" width="22.0"/>
-    <col customWidth="1" min="13" max="13" width="34.0"/>
-    <col customWidth="1" min="14" max="26" width="8.75"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="6" width="32" customWidth="1"/>
+    <col min="7" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="38" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="34" customWidth="1"/>
+    <col min="14" max="26" width="8.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.0" customHeight="1">
+    <row r="1" spans="1:13" ht="27" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3119,7 +3277,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="33.0" customHeight="1">
+    <row r="2" spans="1:13" ht="33" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>50</v>
       </c>
@@ -3142,7 +3300,7 @@
         <v>12</v>
       </c>
       <c r="H2" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>55</v>
@@ -3158,7 +3316,7 @@
       </c>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" ht="33.0" customHeight="1">
+    <row r="3" spans="1:13" ht="33" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>56</v>
       </c>
@@ -3181,7 +3339,7 @@
         <v>12</v>
       </c>
       <c r="H3" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>60</v>
@@ -3197,7 +3355,7 @@
       </c>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" ht="33.0" customHeight="1">
+    <row r="4" spans="1:13" ht="33" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>61</v>
       </c>
@@ -3220,7 +3378,7 @@
         <v>12</v>
       </c>
       <c r="H4" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>65</v>
@@ -3236,7 +3394,7 @@
       </c>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" ht="33.0" customHeight="1">
+    <row r="5" spans="1:13" ht="33" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>66</v>
       </c>
@@ -3259,7 +3417,7 @@
         <v>12</v>
       </c>
       <c r="H5" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>70</v>
@@ -3275,7 +3433,7 @@
       </c>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" ht="33.0" customHeight="1">
+    <row r="6" spans="1:13" ht="33" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>71</v>
       </c>
@@ -3298,7 +3456,7 @@
         <v>12</v>
       </c>
       <c r="H6" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>75</v>
@@ -3314,7 +3472,7 @@
       </c>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" ht="33.0" customHeight="1">
+    <row r="7" spans="1:13" ht="33" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -3337,7 +3495,7 @@
         <v>12</v>
       </c>
       <c r="H7" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>80</v>
@@ -3353,7 +3511,7 @@
       </c>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" ht="33.0" customHeight="1">
+    <row r="8" spans="1:13" ht="33" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>81</v>
       </c>
@@ -3376,7 +3534,7 @@
         <v>12</v>
       </c>
       <c r="H8" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>86</v>
@@ -3392,7 +3550,7 @@
       </c>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" ht="33.0" customHeight="1">
+    <row r="9" spans="1:13" ht="33" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>87</v>
       </c>
@@ -3415,7 +3573,7 @@
         <v>12</v>
       </c>
       <c r="H9" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>91</v>
@@ -3431,7 +3589,7 @@
       </c>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" ht="33.0" customHeight="1">
+    <row r="10" spans="1:13" ht="33" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>92</v>
       </c>
@@ -3454,7 +3612,7 @@
         <v>12</v>
       </c>
       <c r="H10" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>96</v>
@@ -3470,7 +3628,7 @@
       </c>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" ht="33.0" customHeight="1">
+    <row r="11" spans="1:13" ht="33" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>97</v>
       </c>
@@ -3493,7 +3651,7 @@
         <v>12</v>
       </c>
       <c r="H11" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>101</v>
@@ -3509,7 +3667,7 @@
       </c>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" ht="33.0" customHeight="1">
+    <row r="12" spans="1:13" ht="33" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>102</v>
       </c>
@@ -3532,7 +3690,7 @@
         <v>12</v>
       </c>
       <c r="H12" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>106</v>
@@ -3548,7 +3706,7 @@
       </c>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" ht="33.0" customHeight="1">
+    <row r="13" spans="1:13" ht="33" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>107</v>
       </c>
@@ -3571,7 +3729,7 @@
         <v>12</v>
       </c>
       <c r="H13" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>111</v>
@@ -3587,7 +3745,7 @@
       </c>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" ht="33.0" customHeight="1">
+    <row r="14" spans="1:13" ht="33" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>112</v>
       </c>
@@ -3606,7 +3764,7 @@
         <v>12</v>
       </c>
       <c r="H14" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>114</v>
@@ -3622,7 +3780,7 @@
       </c>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" ht="33.0" customHeight="1">
+    <row r="15" spans="1:13" ht="33" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>115</v>
       </c>
@@ -3645,7 +3803,7 @@
         <v>12</v>
       </c>
       <c r="H15" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>119</v>
@@ -3661,7 +3819,7 @@
       </c>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" ht="33.0" customHeight="1">
+    <row r="16" spans="1:13" ht="33" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>120</v>
       </c>
@@ -3684,7 +3842,7 @@
         <v>12</v>
       </c>
       <c r="H16" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>124</v>
@@ -3700,7 +3858,7 @@
       </c>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" ht="33.0" customHeight="1">
+    <row r="17" spans="1:13" ht="33" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>125</v>
       </c>
@@ -3723,7 +3881,7 @@
         <v>12</v>
       </c>
       <c r="H17" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>129</v>
@@ -3739,7 +3897,7 @@
       </c>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" ht="33.0" customHeight="1">
+    <row r="18" spans="1:13" ht="33" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>130</v>
       </c>
@@ -3762,7 +3920,7 @@
         <v>12</v>
       </c>
       <c r="H18" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>134</v>
@@ -3778,7 +3936,7 @@
       </c>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" ht="33.0" customHeight="1">
+    <row r="19" spans="1:13" ht="33" customHeight="1">
       <c r="A19" s="7" t="s">
         <v>135</v>
       </c>
@@ -3801,7 +3959,7 @@
         <v>12</v>
       </c>
       <c r="H19" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>139</v>
@@ -3817,7 +3975,7 @@
       </c>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" ht="33.0" customHeight="1">
+    <row r="20" spans="1:13" ht="33" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>140</v>
       </c>
@@ -3840,7 +3998,7 @@
         <v>12</v>
       </c>
       <c r="H20" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>144</v>
@@ -3856,7 +4014,7 @@
       </c>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" ht="33.0" customHeight="1">
+    <row r="21" spans="1:13" ht="33" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>145</v>
       </c>
@@ -3879,7 +4037,7 @@
         <v>12</v>
       </c>
       <c r="H21" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>149</v>
@@ -3895,7 +4053,7 @@
       </c>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" ht="33.0" customHeight="1">
+    <row r="22" spans="1:13" ht="33" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>150</v>
       </c>
@@ -3918,7 +4076,7 @@
         <v>12</v>
       </c>
       <c r="H22" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>154</v>
@@ -3934,37 +4092,85 @@
       </c>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" ht="33.0" customHeight="1">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="3"/>
+    <row r="23" spans="1:13" ht="33" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="4">
+        <v>3</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" ht="33.0" customHeight="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="3"/>
+    <row r="24" spans="1:13" ht="33" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="4">
+        <v>4</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" ht="33.0" customHeight="1">
+    <row r="25" spans="1:13" ht="33" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="3"/>
@@ -3979,7 +4185,7 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" ht="33.0" customHeight="1">
+    <row r="26" spans="1:13" ht="33" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="3"/>
@@ -3994,7 +4200,7 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" ht="33.0" customHeight="1">
+    <row r="27" spans="1:13" ht="33" customHeight="1">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="3"/>
@@ -4009,7 +4215,7 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" ht="33.0" customHeight="1">
+    <row r="28" spans="1:13" ht="33" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="3"/>
@@ -4024,7 +4230,7 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" ht="33.0" customHeight="1">
+    <row r="29" spans="1:13" ht="33" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="3"/>
@@ -4039,7 +4245,7 @@
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" ht="33.0" customHeight="1">
+    <row r="30" spans="1:13" ht="33" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="3"/>
@@ -4054,7 +4260,7 @@
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" ht="33.0" customHeight="1">
+    <row r="31" spans="1:13" ht="33" customHeight="1">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
@@ -4069,7 +4275,7 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" ht="33.0" customHeight="1">
+    <row r="32" spans="1:13" ht="33" customHeight="1">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="3"/>
@@ -4084,7 +4290,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" ht="33.0" customHeight="1">
+    <row r="33" spans="1:13" ht="33" customHeight="1">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="3"/>
@@ -4099,7 +4305,7 @@
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" ht="33.0" customHeight="1">
+    <row r="34" spans="1:13" ht="33" customHeight="1">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="3"/>
@@ -4114,7 +4320,7 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" ht="33.0" customHeight="1">
+    <row r="35" spans="1:13" ht="33" customHeight="1">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="3"/>
@@ -4129,7 +4335,7 @@
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" ht="33.0" customHeight="1">
+    <row r="36" spans="1:13" ht="33" customHeight="1">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
@@ -4144,7 +4350,7 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" ht="33.0" customHeight="1">
+    <row r="37" spans="1:13" ht="33" customHeight="1">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="3"/>
@@ -4159,7 +4365,7 @@
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" ht="33.0" customHeight="1">
+    <row r="38" spans="1:13" ht="33" customHeight="1">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="3"/>
@@ -4174,7 +4380,7 @@
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" ht="33.0" customHeight="1">
+    <row r="39" spans="1:13" ht="33" customHeight="1">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="3"/>
@@ -4189,7 +4395,7 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" ht="33.0" customHeight="1">
+    <row r="40" spans="1:13" ht="33" customHeight="1">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
@@ -4204,7 +4410,7 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" ht="33.0" customHeight="1">
+    <row r="41" spans="1:13" ht="33" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="3"/>
@@ -4219,7 +4425,7 @@
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" ht="33.0" customHeight="1">
+    <row r="42" spans="1:13" ht="33" customHeight="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="3"/>
@@ -4234,7 +4440,7 @@
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" ht="33.0" customHeight="1">
+    <row r="43" spans="1:13" ht="33" customHeight="1">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="3"/>
@@ -4249,7 +4455,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" ht="33.0" customHeight="1">
+    <row r="44" spans="1:13" ht="33" customHeight="1">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="3"/>
@@ -4264,7 +4470,7 @@
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" ht="33.0" customHeight="1">
+    <row r="45" spans="1:13" ht="33" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="3"/>
@@ -4279,7 +4485,7 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" ht="33.0" customHeight="1">
+    <row r="46" spans="1:13" ht="33" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="3"/>
@@ -4294,7 +4500,7 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" ht="33.0" customHeight="1">
+    <row r="47" spans="1:13" ht="33" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="3"/>
@@ -4309,7 +4515,7 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" ht="33.0" customHeight="1">
+    <row r="48" spans="1:13" ht="33" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="3"/>
@@ -4324,7 +4530,7 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" ht="33.0" customHeight="1">
+    <row r="49" spans="1:13" ht="33" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="3"/>
@@ -4339,7 +4545,7 @@
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" ht="33.0" customHeight="1">
+    <row r="50" spans="1:13" ht="33" customHeight="1">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="3"/>
@@ -4354,7 +4560,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" ht="33.0" customHeight="1">
+    <row r="51" spans="1:13" ht="33" customHeight="1">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="3"/>
@@ -4369,7 +4575,7 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" ht="33.0" customHeight="1">
+    <row r="52" spans="1:13" ht="33" customHeight="1">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="3"/>
@@ -4384,7 +4590,7 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" ht="33.0" customHeight="1">
+    <row r="53" spans="1:13" ht="33" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="3"/>
@@ -4399,7 +4605,7 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" ht="33.0" customHeight="1">
+    <row r="54" spans="1:13" ht="33" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="3"/>
@@ -4414,7 +4620,7 @@
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" ht="33.0" customHeight="1">
+    <row r="55" spans="1:13" ht="33" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="3"/>
@@ -4429,7 +4635,7 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" ht="33.0" customHeight="1">
+    <row r="56" spans="1:13" ht="33" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="3"/>
@@ -4444,7 +4650,7 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" ht="33.0" customHeight="1">
+    <row r="57" spans="1:13" ht="33" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="3"/>
@@ -4459,7 +4665,7 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" ht="33.0" customHeight="1">
+    <row r="58" spans="1:13" ht="33" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="3"/>
@@ -4474,7 +4680,7 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" ht="33.0" customHeight="1">
+    <row r="59" spans="1:13" ht="33" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="3"/>
@@ -4489,7 +4695,7 @@
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" ht="33.0" customHeight="1">
+    <row r="60" spans="1:13" ht="33" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="3"/>
@@ -4504,7 +4710,7 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" ht="33.0" customHeight="1">
+    <row r="61" spans="1:13" ht="33" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="3"/>
@@ -4519,7 +4725,7 @@
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
     </row>
-    <row r="62" ht="33.0" customHeight="1">
+    <row r="62" spans="1:13" ht="33" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="3"/>
@@ -4534,7 +4740,7 @@
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" ht="33.0" customHeight="1">
+    <row r="63" spans="1:13" ht="33" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="3"/>
@@ -4549,7 +4755,7 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" ht="33.0" customHeight="1">
+    <row r="64" spans="1:13" ht="33" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="3"/>
@@ -4564,7 +4770,7 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
     </row>
-    <row r="65" ht="33.0" customHeight="1">
+    <row r="65" spans="1:13" ht="33" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="3"/>
@@ -4579,7 +4785,7 @@
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" ht="33.0" customHeight="1">
+    <row r="66" spans="1:13" ht="33" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="3"/>
@@ -4594,7 +4800,7 @@
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
     </row>
-    <row r="67" ht="33.0" customHeight="1">
+    <row r="67" spans="1:13" ht="33" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="3"/>
@@ -4609,7 +4815,7 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" ht="33.0" customHeight="1">
+    <row r="68" spans="1:13" ht="33" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="3"/>
@@ -4624,7 +4830,7 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" ht="33.0" customHeight="1">
+    <row r="69" spans="1:13" ht="33" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="3"/>
@@ -4639,7 +4845,7 @@
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
     </row>
-    <row r="70" ht="33.0" customHeight="1">
+    <row r="70" spans="1:13" ht="33" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="3"/>
@@ -4654,7 +4860,7 @@
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
     </row>
-    <row r="71" ht="33.0" customHeight="1">
+    <row r="71" spans="1:13" ht="33" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="3"/>
@@ -4669,7 +4875,7 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
     </row>
-    <row r="72" ht="33.0" customHeight="1">
+    <row r="72" spans="1:13" ht="33" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="3"/>
@@ -4684,7 +4890,7 @@
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
     </row>
-    <row r="73" ht="33.0" customHeight="1">
+    <row r="73" spans="1:13" ht="33" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="3"/>
@@ -4699,7 +4905,7 @@
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
     </row>
-    <row r="74" ht="33.0" customHeight="1">
+    <row r="74" spans="1:13" ht="33" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="3"/>
@@ -4714,7 +4920,7 @@
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
     </row>
-    <row r="75" ht="33.0" customHeight="1">
+    <row r="75" spans="1:13" ht="33" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="3"/>
@@ -4729,7 +4935,7 @@
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
     </row>
-    <row r="76" ht="33.0" customHeight="1">
+    <row r="76" spans="1:13" ht="33" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="3"/>
@@ -4744,7 +4950,7 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" ht="33.0" customHeight="1">
+    <row r="77" spans="1:13" ht="33" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="3"/>
@@ -4759,7 +4965,7 @@
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
     </row>
-    <row r="78" ht="33.0" customHeight="1">
+    <row r="78" spans="1:13" ht="33" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="3"/>
@@ -4774,7 +4980,7 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
     </row>
-    <row r="79" ht="33.0" customHeight="1">
+    <row r="79" spans="1:13" ht="33" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="3"/>
@@ -4789,7 +4995,7 @@
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
     </row>
-    <row r="80" ht="33.0" customHeight="1">
+    <row r="80" spans="1:13" ht="33" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="3"/>
@@ -4804,7 +5010,7 @@
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
     </row>
-    <row r="81" ht="33.0" customHeight="1">
+    <row r="81" spans="1:13" ht="33" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="3"/>
@@ -4819,7 +5025,7 @@
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
     </row>
-    <row r="82" ht="33.0" customHeight="1">
+    <row r="82" spans="1:13" ht="33" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="3"/>
@@ -4834,7 +5040,7 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
     </row>
-    <row r="83" ht="33.0" customHeight="1">
+    <row r="83" spans="1:13" ht="33" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="3"/>
@@ -4849,7 +5055,7 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
     </row>
-    <row r="84" ht="33.0" customHeight="1">
+    <row r="84" spans="1:13" ht="33" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="3"/>
@@ -4864,7 +5070,7 @@
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
     </row>
-    <row r="85" ht="33.0" customHeight="1">
+    <row r="85" spans="1:13" ht="33" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="3"/>
@@ -4879,7 +5085,7 @@
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
     </row>
-    <row r="86" ht="33.0" customHeight="1">
+    <row r="86" spans="1:13" ht="33" customHeight="1">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="3"/>
@@ -4894,7 +5100,7 @@
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
     </row>
-    <row r="87" ht="33.0" customHeight="1">
+    <row r="87" spans="1:13" ht="33" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="3"/>
@@ -4909,7 +5115,7 @@
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
     </row>
-    <row r="88" ht="33.0" customHeight="1">
+    <row r="88" spans="1:13" ht="33" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="3"/>
@@ -4924,7 +5130,7 @@
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
     </row>
-    <row r="89" ht="33.0" customHeight="1">
+    <row r="89" spans="1:13" ht="33" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="3"/>
@@ -4939,7 +5145,7 @@
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
     </row>
-    <row r="90" ht="33.0" customHeight="1">
+    <row r="90" spans="1:13" ht="33" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="3"/>
@@ -4954,7 +5160,7 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
     </row>
-    <row r="91" ht="33.0" customHeight="1">
+    <row r="91" spans="1:13" ht="33" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="3"/>
@@ -4969,7 +5175,7 @@
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
     </row>
-    <row r="92" ht="33.0" customHeight="1">
+    <row r="92" spans="1:13" ht="33" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="3"/>
@@ -4984,7 +5190,7 @@
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
     </row>
-    <row r="93" ht="33.0" customHeight="1">
+    <row r="93" spans="1:13" ht="33" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="3"/>
@@ -4999,7 +5205,7 @@
       <c r="L93" s="3"/>
       <c r="M93" s="3"/>
     </row>
-    <row r="94" ht="33.0" customHeight="1">
+    <row r="94" spans="1:13" ht="33" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="3"/>
@@ -5014,7 +5220,7 @@
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
     </row>
-    <row r="95" ht="33.0" customHeight="1">
+    <row r="95" spans="1:13" ht="33" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="3"/>
@@ -5029,7 +5235,7 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
     </row>
-    <row r="96" ht="33.0" customHeight="1">
+    <row r="96" spans="1:13" ht="33" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="3"/>
@@ -5044,7 +5250,7 @@
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
     </row>
-    <row r="97" ht="33.0" customHeight="1">
+    <row r="97" spans="1:13" ht="33" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="3"/>
@@ -5059,7 +5265,7 @@
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
     </row>
-    <row r="98" ht="33.0" customHeight="1">
+    <row r="98" spans="1:13" ht="33" customHeight="1">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="3"/>
@@ -5074,7 +5280,7 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
     </row>
-    <row r="99" ht="33.0" customHeight="1">
+    <row r="99" spans="1:13" ht="33" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="3"/>
@@ -5089,7 +5295,7 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
     </row>
-    <row r="100" ht="33.0" customHeight="1">
+    <row r="100" spans="1:13" ht="33" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="3"/>
@@ -5104,7 +5310,7 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
     </row>
-    <row r="101" ht="33.0" customHeight="1">
+    <row r="101" spans="1:13" ht="33" customHeight="1">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="3"/>
@@ -5119,7 +5325,7 @@
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
     </row>
-    <row r="102" ht="33.0" customHeight="1">
+    <row r="102" spans="1:13" ht="33" customHeight="1">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="3"/>
@@ -5134,7 +5340,7 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
     </row>
-    <row r="103" ht="33.0" customHeight="1">
+    <row r="103" spans="1:13" ht="33" customHeight="1">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="3"/>
@@ -5149,7 +5355,7 @@
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
     </row>
-    <row r="104" ht="33.0" customHeight="1">
+    <row r="104" spans="1:13" ht="33" customHeight="1">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="3"/>
@@ -5164,7 +5370,7 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
     </row>
-    <row r="105" ht="33.0" customHeight="1">
+    <row r="105" spans="1:13" ht="33" customHeight="1">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="3"/>
@@ -5179,7 +5385,7 @@
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
     </row>
-    <row r="106" ht="33.0" customHeight="1">
+    <row r="106" spans="1:13" ht="33" customHeight="1">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="3"/>
@@ -5194,7 +5400,7 @@
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
     </row>
-    <row r="107" ht="33.0" customHeight="1">
+    <row r="107" spans="1:13" ht="33" customHeight="1">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="3"/>
@@ -5209,7 +5415,7 @@
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
     </row>
-    <row r="108" ht="33.0" customHeight="1">
+    <row r="108" spans="1:13" ht="33" customHeight="1">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="3"/>
@@ -5224,7 +5430,7 @@
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
     </row>
-    <row r="109" ht="33.0" customHeight="1">
+    <row r="109" spans="1:13" ht="33" customHeight="1">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="3"/>
@@ -5239,7 +5445,7 @@
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
     </row>
-    <row r="110" ht="33.0" customHeight="1">
+    <row r="110" spans="1:13" ht="33" customHeight="1">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="3"/>
@@ -5254,7 +5460,7 @@
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
     </row>
-    <row r="111" ht="33.0" customHeight="1">
+    <row r="111" spans="1:13" ht="33" customHeight="1">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="3"/>
@@ -5269,7 +5475,7 @@
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
     </row>
-    <row r="112" ht="33.0" customHeight="1">
+    <row r="112" spans="1:13" ht="33" customHeight="1">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="3"/>
@@ -5284,7 +5490,7 @@
       <c r="L112" s="3"/>
       <c r="M112" s="3"/>
     </row>
-    <row r="113" ht="33.0" customHeight="1">
+    <row r="113" spans="1:13" ht="33" customHeight="1">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="3"/>
@@ -5299,7 +5505,7 @@
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
     </row>
-    <row r="114" ht="33.0" customHeight="1">
+    <row r="114" spans="1:13" ht="33" customHeight="1">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="3"/>
@@ -5314,7 +5520,7 @@
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
     </row>
-    <row r="115" ht="33.0" customHeight="1">
+    <row r="115" spans="1:13" ht="33" customHeight="1">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="3"/>
@@ -5329,7 +5535,7 @@
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
     </row>
-    <row r="116" ht="33.0" customHeight="1">
+    <row r="116" spans="1:13" ht="33" customHeight="1">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="3"/>
@@ -5344,7 +5550,7 @@
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
     </row>
-    <row r="117" ht="33.0" customHeight="1">
+    <row r="117" spans="1:13" ht="33" customHeight="1">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="3"/>
@@ -5359,7 +5565,7 @@
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
     </row>
-    <row r="118" ht="33.0" customHeight="1">
+    <row r="118" spans="1:13" ht="33" customHeight="1">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="3"/>
@@ -5374,7 +5580,7 @@
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
     </row>
-    <row r="119" ht="33.0" customHeight="1">
+    <row r="119" spans="1:13" ht="33" customHeight="1">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="3"/>
@@ -5389,7 +5595,7 @@
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
     </row>
-    <row r="120" ht="33.0" customHeight="1">
+    <row r="120" spans="1:13" ht="33" customHeight="1">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="3"/>
@@ -5404,7 +5610,7 @@
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
     </row>
-    <row r="121" ht="33.0" customHeight="1">
+    <row r="121" spans="1:13" ht="33" customHeight="1">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="3"/>
@@ -5419,7 +5625,7 @@
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
     </row>
-    <row r="122" ht="33.0" customHeight="1">
+    <row r="122" spans="1:13" ht="33" customHeight="1">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="3"/>
@@ -5434,7 +5640,7 @@
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" ht="33.0" customHeight="1">
+    <row r="123" spans="1:13" ht="33" customHeight="1">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="3"/>
@@ -5449,7 +5655,7 @@
       <c r="L123" s="3"/>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" ht="33.0" customHeight="1">
+    <row r="124" spans="1:13" ht="33" customHeight="1">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="3"/>
@@ -5464,7 +5670,7 @@
       <c r="L124" s="3"/>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" ht="33.0" customHeight="1">
+    <row r="125" spans="1:13" ht="33" customHeight="1">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="3"/>
@@ -5479,7 +5685,7 @@
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" ht="33.0" customHeight="1">
+    <row r="126" spans="1:13" ht="33" customHeight="1">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="3"/>
@@ -5494,7 +5700,7 @@
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" ht="33.0" customHeight="1">
+    <row r="127" spans="1:13" ht="33" customHeight="1">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="3"/>
@@ -5509,7 +5715,7 @@
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" ht="33.0" customHeight="1">
+    <row r="128" spans="1:13" ht="33" customHeight="1">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="3"/>
@@ -5524,7 +5730,7 @@
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
     </row>
-    <row r="129" ht="33.0" customHeight="1">
+    <row r="129" spans="1:13" ht="33" customHeight="1">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="3"/>
@@ -5539,7 +5745,7 @@
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
     </row>
-    <row r="130" ht="33.0" customHeight="1">
+    <row r="130" spans="1:13" ht="33" customHeight="1">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="3"/>
@@ -5554,7 +5760,7 @@
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" ht="33.0" customHeight="1">
+    <row r="131" spans="1:13" ht="33" customHeight="1">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="3"/>
@@ -5569,7 +5775,7 @@
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
     </row>
-    <row r="132" ht="33.0" customHeight="1">
+    <row r="132" spans="1:13" ht="33" customHeight="1">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="3"/>
@@ -5584,7 +5790,7 @@
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
     </row>
-    <row r="133" ht="33.0" customHeight="1">
+    <row r="133" spans="1:13" ht="33" customHeight="1">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="3"/>
@@ -5599,7 +5805,7 @@
       <c r="L133" s="3"/>
       <c r="M133" s="3"/>
     </row>
-    <row r="134" ht="33.0" customHeight="1">
+    <row r="134" spans="1:13" ht="33" customHeight="1">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="3"/>
@@ -5614,7 +5820,7 @@
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
     </row>
-    <row r="135" ht="33.0" customHeight="1">
+    <row r="135" spans="1:13" ht="33" customHeight="1">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="3"/>
@@ -5629,7 +5835,7 @@
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
     </row>
-    <row r="136" ht="33.0" customHeight="1">
+    <row r="136" spans="1:13" ht="33" customHeight="1">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="3"/>
@@ -5644,7 +5850,7 @@
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
     </row>
-    <row r="137" ht="33.0" customHeight="1">
+    <row r="137" spans="1:13" ht="33" customHeight="1">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="3"/>
@@ -5659,7 +5865,7 @@
       <c r="L137" s="3"/>
       <c r="M137" s="3"/>
     </row>
-    <row r="138" ht="33.0" customHeight="1">
+    <row r="138" spans="1:13" ht="33" customHeight="1">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="3"/>
@@ -5674,7 +5880,7 @@
       <c r="L138" s="3"/>
       <c r="M138" s="3"/>
     </row>
-    <row r="139" ht="33.0" customHeight="1">
+    <row r="139" spans="1:13" ht="33" customHeight="1">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="3"/>
@@ -5689,7 +5895,7 @@
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
     </row>
-    <row r="140" ht="33.0" customHeight="1">
+    <row r="140" spans="1:13" ht="33" customHeight="1">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="3"/>
@@ -5704,7 +5910,7 @@
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
     </row>
-    <row r="141" ht="33.0" customHeight="1">
+    <row r="141" spans="1:13" ht="33" customHeight="1">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="3"/>
@@ -5719,7 +5925,7 @@
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
     </row>
-    <row r="142" ht="33.0" customHeight="1">
+    <row r="142" spans="1:13" ht="33" customHeight="1">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="3"/>
@@ -5734,7 +5940,7 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
     </row>
-    <row r="143" ht="33.0" customHeight="1">
+    <row r="143" spans="1:13" ht="33" customHeight="1">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="3"/>
@@ -5749,7 +5955,7 @@
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
     </row>
-    <row r="144" ht="33.0" customHeight="1">
+    <row r="144" spans="1:13" ht="33" customHeight="1">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="3"/>
@@ -5764,7 +5970,7 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
     </row>
-    <row r="145" ht="33.0" customHeight="1">
+    <row r="145" spans="1:13" ht="33" customHeight="1">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="3"/>
@@ -5779,7 +5985,7 @@
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
     </row>
-    <row r="146" ht="33.0" customHeight="1">
+    <row r="146" spans="1:13" ht="33" customHeight="1">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="3"/>
@@ -5794,7 +6000,7 @@
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
     </row>
-    <row r="147" ht="33.0" customHeight="1">
+    <row r="147" spans="1:13" ht="33" customHeight="1">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="3"/>
@@ -5809,7 +6015,7 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
     </row>
-    <row r="148" ht="33.0" customHeight="1">
+    <row r="148" spans="1:13" ht="33" customHeight="1">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="3"/>
@@ -5824,7 +6030,7 @@
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
     </row>
-    <row r="149" ht="33.0" customHeight="1">
+    <row r="149" spans="1:13" ht="33" customHeight="1">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="3"/>
@@ -5839,7 +6045,7 @@
       <c r="L149" s="3"/>
       <c r="M149" s="3"/>
     </row>
-    <row r="150" ht="33.0" customHeight="1">
+    <row r="150" spans="1:13" ht="33" customHeight="1">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="3"/>
@@ -5854,7 +6060,7 @@
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
     </row>
-    <row r="151" ht="33.0" customHeight="1">
+    <row r="151" spans="1:13" ht="33" customHeight="1">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="3"/>
@@ -5869,7 +6075,7 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
     </row>
-    <row r="152" ht="33.0" customHeight="1">
+    <row r="152" spans="1:13" ht="33" customHeight="1">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="3"/>
@@ -5884,7 +6090,7 @@
       <c r="L152" s="3"/>
       <c r="M152" s="3"/>
     </row>
-    <row r="153" ht="33.0" customHeight="1">
+    <row r="153" spans="1:13" ht="33" customHeight="1">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="3"/>
@@ -5899,7 +6105,7 @@
       <c r="L153" s="3"/>
       <c r="M153" s="3"/>
     </row>
-    <row r="154" ht="33.0" customHeight="1">
+    <row r="154" spans="1:13" ht="33" customHeight="1">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="3"/>
@@ -5914,7 +6120,7 @@
       <c r="L154" s="3"/>
       <c r="M154" s="3"/>
     </row>
-    <row r="155" ht="33.0" customHeight="1">
+    <row r="155" spans="1:13" ht="33" customHeight="1">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="3"/>
@@ -5929,7 +6135,7 @@
       <c r="L155" s="3"/>
       <c r="M155" s="3"/>
     </row>
-    <row r="156" ht="33.0" customHeight="1">
+    <row r="156" spans="1:13" ht="33" customHeight="1">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="3"/>
@@ -5944,7 +6150,7 @@
       <c r="L156" s="3"/>
       <c r="M156" s="3"/>
     </row>
-    <row r="157" ht="33.0" customHeight="1">
+    <row r="157" spans="1:13" ht="33" customHeight="1">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="3"/>
@@ -5959,7 +6165,7 @@
       <c r="L157" s="3"/>
       <c r="M157" s="3"/>
     </row>
-    <row r="158" ht="33.0" customHeight="1">
+    <row r="158" spans="1:13" ht="33" customHeight="1">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="3"/>
@@ -5974,7 +6180,7 @@
       <c r="L158" s="3"/>
       <c r="M158" s="3"/>
     </row>
-    <row r="159" ht="33.0" customHeight="1">
+    <row r="159" spans="1:13" ht="33" customHeight="1">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="3"/>
@@ -5989,7 +6195,7 @@
       <c r="L159" s="3"/>
       <c r="M159" s="3"/>
     </row>
-    <row r="160" ht="33.0" customHeight="1">
+    <row r="160" spans="1:13" ht="33" customHeight="1">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="3"/>
@@ -6004,7 +6210,7 @@
       <c r="L160" s="3"/>
       <c r="M160" s="3"/>
     </row>
-    <row r="161" ht="33.0" customHeight="1">
+    <row r="161" spans="1:13" ht="33" customHeight="1">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="3"/>
@@ -6019,7 +6225,7 @@
       <c r="L161" s="3"/>
       <c r="M161" s="3"/>
     </row>
-    <row r="162" ht="33.0" customHeight="1">
+    <row r="162" spans="1:13" ht="33" customHeight="1">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="3"/>
@@ -6034,7 +6240,7 @@
       <c r="L162" s="3"/>
       <c r="M162" s="3"/>
     </row>
-    <row r="163" ht="33.0" customHeight="1">
+    <row r="163" spans="1:13" ht="33" customHeight="1">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="3"/>
@@ -6049,7 +6255,7 @@
       <c r="L163" s="3"/>
       <c r="M163" s="3"/>
     </row>
-    <row r="164" ht="33.0" customHeight="1">
+    <row r="164" spans="1:13" ht="33" customHeight="1">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="3"/>
@@ -6064,7 +6270,7 @@
       <c r="L164" s="3"/>
       <c r="M164" s="3"/>
     </row>
-    <row r="165" ht="33.0" customHeight="1">
+    <row r="165" spans="1:13" ht="33" customHeight="1">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="3"/>
@@ -6079,7 +6285,7 @@
       <c r="L165" s="3"/>
       <c r="M165" s="3"/>
     </row>
-    <row r="166" ht="33.0" customHeight="1">
+    <row r="166" spans="1:13" ht="33" customHeight="1">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="3"/>
@@ -6094,7 +6300,7 @@
       <c r="L166" s="3"/>
       <c r="M166" s="3"/>
     </row>
-    <row r="167" ht="33.0" customHeight="1">
+    <row r="167" spans="1:13" ht="33" customHeight="1">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="3"/>
@@ -6109,7 +6315,7 @@
       <c r="L167" s="3"/>
       <c r="M167" s="3"/>
     </row>
-    <row r="168" ht="33.0" customHeight="1">
+    <row r="168" spans="1:13" ht="33" customHeight="1">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="3"/>
@@ -6124,7 +6330,7 @@
       <c r="L168" s="3"/>
       <c r="M168" s="3"/>
     </row>
-    <row r="169" ht="33.0" customHeight="1">
+    <row r="169" spans="1:13" ht="33" customHeight="1">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="3"/>
@@ -6139,7 +6345,7 @@
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
     </row>
-    <row r="170" ht="33.0" customHeight="1">
+    <row r="170" spans="1:13" ht="33" customHeight="1">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="3"/>
@@ -6154,7 +6360,7 @@
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
     </row>
-    <row r="171" ht="33.0" customHeight="1">
+    <row r="171" spans="1:13" ht="33" customHeight="1">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="3"/>
@@ -6169,7 +6375,7 @@
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
     </row>
-    <row r="172" ht="33.0" customHeight="1">
+    <row r="172" spans="1:13" ht="33" customHeight="1">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="3"/>
@@ -6184,7 +6390,7 @@
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
     </row>
-    <row r="173" ht="33.0" customHeight="1">
+    <row r="173" spans="1:13" ht="33" customHeight="1">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="3"/>
@@ -6199,7 +6405,7 @@
       <c r="L173" s="3"/>
       <c r="M173" s="3"/>
     </row>
-    <row r="174" ht="33.0" customHeight="1">
+    <row r="174" spans="1:13" ht="33" customHeight="1">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="3"/>
@@ -6214,7 +6420,7 @@
       <c r="L174" s="3"/>
       <c r="M174" s="3"/>
     </row>
-    <row r="175" ht="33.0" customHeight="1">
+    <row r="175" spans="1:13" ht="33" customHeight="1">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="3"/>
@@ -6229,7 +6435,7 @@
       <c r="L175" s="3"/>
       <c r="M175" s="3"/>
     </row>
-    <row r="176" ht="33.0" customHeight="1">
+    <row r="176" spans="1:13" ht="33" customHeight="1">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="3"/>
@@ -6244,7 +6450,7 @@
       <c r="L176" s="3"/>
       <c r="M176" s="3"/>
     </row>
-    <row r="177" ht="33.0" customHeight="1">
+    <row r="177" spans="1:13" ht="33" customHeight="1">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="3"/>
@@ -6259,7 +6465,7 @@
       <c r="L177" s="3"/>
       <c r="M177" s="3"/>
     </row>
-    <row r="178" ht="33.0" customHeight="1">
+    <row r="178" spans="1:13" ht="33" customHeight="1">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="3"/>
@@ -6274,7 +6480,7 @@
       <c r="L178" s="3"/>
       <c r="M178" s="3"/>
     </row>
-    <row r="179" ht="33.0" customHeight="1">
+    <row r="179" spans="1:13" ht="33" customHeight="1">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="3"/>
@@ -6289,7 +6495,7 @@
       <c r="L179" s="3"/>
       <c r="M179" s="3"/>
     </row>
-    <row r="180" ht="33.0" customHeight="1">
+    <row r="180" spans="1:13" ht="33" customHeight="1">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="3"/>
@@ -6304,7 +6510,7 @@
       <c r="L180" s="3"/>
       <c r="M180" s="3"/>
     </row>
-    <row r="181" ht="33.0" customHeight="1">
+    <row r="181" spans="1:13" ht="33" customHeight="1">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="3"/>
@@ -6319,7 +6525,7 @@
       <c r="L181" s="3"/>
       <c r="M181" s="3"/>
     </row>
-    <row r="182" ht="33.0" customHeight="1">
+    <row r="182" spans="1:13" ht="33" customHeight="1">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="3"/>
@@ -6334,7 +6540,7 @@
       <c r="L182" s="3"/>
       <c r="M182" s="3"/>
     </row>
-    <row r="183" ht="33.0" customHeight="1">
+    <row r="183" spans="1:13" ht="33" customHeight="1">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="3"/>
@@ -6349,7 +6555,7 @@
       <c r="L183" s="3"/>
       <c r="M183" s="3"/>
     </row>
-    <row r="184" ht="33.0" customHeight="1">
+    <row r="184" spans="1:13" ht="33" customHeight="1">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="3"/>
@@ -6364,7 +6570,7 @@
       <c r="L184" s="3"/>
       <c r="M184" s="3"/>
     </row>
-    <row r="185" ht="33.0" customHeight="1">
+    <row r="185" spans="1:13" ht="33" customHeight="1">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="3"/>
@@ -6379,7 +6585,7 @@
       <c r="L185" s="3"/>
       <c r="M185" s="3"/>
     </row>
-    <row r="186" ht="33.0" customHeight="1">
+    <row r="186" spans="1:13" ht="33" customHeight="1">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="3"/>
@@ -6394,7 +6600,7 @@
       <c r="L186" s="3"/>
       <c r="M186" s="3"/>
     </row>
-    <row r="187" ht="33.0" customHeight="1">
+    <row r="187" spans="1:13" ht="33" customHeight="1">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="3"/>
@@ -6409,7 +6615,7 @@
       <c r="L187" s="3"/>
       <c r="M187" s="3"/>
     </row>
-    <row r="188" ht="33.0" customHeight="1">
+    <row r="188" spans="1:13" ht="33" customHeight="1">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="3"/>
@@ -6424,7 +6630,7 @@
       <c r="L188" s="3"/>
       <c r="M188" s="3"/>
     </row>
-    <row r="189" ht="33.0" customHeight="1">
+    <row r="189" spans="1:13" ht="33" customHeight="1">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="3"/>
@@ -6439,7 +6645,7 @@
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
     </row>
-    <row r="190" ht="33.0" customHeight="1">
+    <row r="190" spans="1:13" ht="33" customHeight="1">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="3"/>
@@ -6454,7 +6660,7 @@
       <c r="L190" s="3"/>
       <c r="M190" s="3"/>
     </row>
-    <row r="191" ht="33.0" customHeight="1">
+    <row r="191" spans="1:13" ht="33" customHeight="1">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="3"/>
@@ -6469,7 +6675,7 @@
       <c r="L191" s="3"/>
       <c r="M191" s="3"/>
     </row>
-    <row r="192" ht="33.0" customHeight="1">
+    <row r="192" spans="1:13" ht="33" customHeight="1">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="3"/>
@@ -6484,7 +6690,7 @@
       <c r="L192" s="3"/>
       <c r="M192" s="3"/>
     </row>
-    <row r="193" ht="33.0" customHeight="1">
+    <row r="193" spans="1:13" ht="33" customHeight="1">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="3"/>
@@ -6499,7 +6705,7 @@
       <c r="L193" s="3"/>
       <c r="M193" s="3"/>
     </row>
-    <row r="194" ht="33.0" customHeight="1">
+    <row r="194" spans="1:13" ht="33" customHeight="1">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="3"/>
@@ -6514,7 +6720,7 @@
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
     </row>
-    <row r="195" ht="33.0" customHeight="1">
+    <row r="195" spans="1:13" ht="33" customHeight="1">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="3"/>
@@ -6529,7 +6735,7 @@
       <c r="L195" s="3"/>
       <c r="M195" s="3"/>
     </row>
-    <row r="196" ht="33.0" customHeight="1">
+    <row r="196" spans="1:13" ht="33" customHeight="1">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="3"/>
@@ -6544,7 +6750,7 @@
       <c r="L196" s="3"/>
       <c r="M196" s="3"/>
     </row>
-    <row r="197" ht="33.0" customHeight="1">
+    <row r="197" spans="1:13" ht="33" customHeight="1">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="3"/>
@@ -6559,7 +6765,7 @@
       <c r="L197" s="3"/>
       <c r="M197" s="3"/>
     </row>
-    <row r="198" ht="33.0" customHeight="1">
+    <row r="198" spans="1:13" ht="33" customHeight="1">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="3"/>
@@ -6574,7 +6780,7 @@
       <c r="L198" s="3"/>
       <c r="M198" s="3"/>
     </row>
-    <row r="199" ht="33.0" customHeight="1">
+    <row r="199" spans="1:13" ht="33" customHeight="1">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="3"/>
@@ -6589,7 +6795,7 @@
       <c r="L199" s="3"/>
       <c r="M199" s="3"/>
     </row>
-    <row r="200" ht="33.0" customHeight="1">
+    <row r="200" spans="1:13" ht="33" customHeight="1">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="3"/>
@@ -6604,7 +6810,7 @@
       <c r="L200" s="3"/>
       <c r="M200" s="3"/>
     </row>
-    <row r="201" ht="33.0" customHeight="1">
+    <row r="201" spans="1:13" ht="33" customHeight="1">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="3"/>
@@ -6619,13 +6825,13 @@
       <c r="L201" s="3"/>
       <c r="M201" s="3"/>
     </row>
-    <row r="202" ht="14.25" customHeight="1"/>
-    <row r="203" ht="14.25" customHeight="1"/>
-    <row r="204" ht="14.25" customHeight="1"/>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="202" spans="1:13" ht="14.25" customHeight="1"/>
+    <row r="203" spans="1:13" ht="14.25" customHeight="1"/>
+    <row r="204" spans="1:13" ht="14.25" customHeight="1"/>
+    <row r="205" spans="1:13" ht="14.25" customHeight="1"/>
+    <row r="206" spans="1:13" ht="14.25" customHeight="1"/>
+    <row r="207" spans="1:13" ht="14.25" customHeight="1"/>
+    <row r="208" spans="1:13" ht="14.25" customHeight="1"/>
     <row r="209" ht="14.25" customHeight="1"/>
     <row r="210" ht="14.25" customHeight="1"/>
     <row r="211" ht="14.25" customHeight="1"/>
@@ -7420,65 +7626,62 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="G2:G201">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>G2="Alta"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G201">
     <cfRule type="expression" dxfId="6" priority="2">
       <formula>G2="Media"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G201">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>G2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J201">
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>J2="Finalizada"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J201">
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>J2="Bloqueada"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K201">
-    <cfRule type="expression" dxfId="7" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>K2="Aprobada"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K201">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>K2="Con observaciones"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K201">
-    <cfRule type="expression" dxfId="5" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>K2="Rechazada"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G201">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G201" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K201">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K201" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Pendiente,Aprobada,Con observaciones,Rechazada"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J201">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J201" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Pendiente,En análisis,Lista,En desarrollo,En revisión,Finalizada,Bloqueada"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17:B201">
-      <formula1>Epicas!$B$2:$B$101</formula1>
-    </dataValidation>
   </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000003000000}">
+          <x14:formula1>
+            <xm:f>Epicas!$B$2:$B$101</xm:f>
+          </x14:formula1>
+          <xm:sqref>B17:B22 B24:B201</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>